--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.11.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.11.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -851,7 +851,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.11.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.11.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,13 +431,13 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="39" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="29" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
     <col width="29" customWidth="1" min="21" max="21"/>
     <col width="31" customWidth="1" min="22" max="22"/>
@@ -601,16 +601,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L1: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: " LETARGE vS. DE TUYLL,â€” Grant's Chancery</t>
+          <t>L84: stray/suspicious non-ASCII glyph(s): U+5E38 CJK UNIFIED IDEOGRAPH-5E38 | isolated marker/symbol line :: 常</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L7: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN, U+2122 TRADE MARK SIGN :: â€¢ LETARGE vs. DE Tuyll,â€”Grantâ€™s Chancery Reports,Vol. 1, p. 227 ;</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]by</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]by</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L10: isolated marker/symbol line :: v.</t>
@@ -624,7 +628,11 @@
       <c r="P2" s="1" t="inlineStr"/>
       <c r="Q2" s="1" t="inlineStr"/>
       <c r="R2" s="1" t="inlineStr"/>
-      <c r="S2" s="1" t="inlineStr"/>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>L7: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • LETARGE vs. DE Tuyll,—Grant’s Chancery Reports,Vol. 1, p. 227 ;</t>
+        </is>
+      </c>
       <c r="T2" s="1" t="inlineStr"/>
       <c r="U2" s="1" t="inlineStr"/>
       <c r="V2" s="1" t="inlineStr"/>
@@ -645,7 +653,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>72</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -658,14 +666,10 @@
         </is>
       </c>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L51: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): HoRToN (odd internal casing) :: JART, vs. HoRToN,â€” Grant's Chancery</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L11: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: words of the conveyanceâ€”in short, where the Statute of Frauds</t>
+          <t>L7: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • LETARGE vs. DE Tuyll,—Grant’s Chancery Reports,Vol. 1, p. 227 ;</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -717,16 +721,8 @@
         </is>
       </c>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L82: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: BRENNAN,â€” Grant's Chancery Reports, V</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L26: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: the reader is referred to STUART, VS. HORTON,â€”Grant's Chancery</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
@@ -754,12 +750,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -768,20 +764,12 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr">
         <is>
-          <t>L51: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): HoRToN (odd internal casing) :: JART, vs. HoRToN,â€” Grant's Chancery</t>
+          <t>L51: suspicious token(s): HoRToN (odd internal casing) :: JART, vs. HoRToN,— Grant's Chancery</t>
         </is>
       </c>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L84: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA | isolated marker/symbol line :: å¸¸</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L43: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: BRENNAN,â€”Grantâ€™s Chancery Reports, Vol.1, p. 371.</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
@@ -833,7 +821,7 @@
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L84: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA | isolated marker/symbol line :: å¸¸</t>
+          <t>L84: stray/suspicious non-ASCII glyph(s): U+5E38 CJK UNIFIED IDEOGRAPH-5E38 | isolated marker/symbol line :: 常</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr"/>
@@ -981,12 +969,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1025,7 +1013,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1142,7 +1130,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
